--- a/从零开始学Slots/从零开始学Slots-18-基础篇-Cascading消除图标.xlsx
+++ b/从零开始学Slots/从零开始学Slots-18-基础篇-Cascading消除图标.xlsx
@@ -6336,6 +6336,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N145" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -7073,5 +7076,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:U76" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-18-基础篇-Cascading消除图标.xlsx
+++ b/从零开始学Slots/从零开始学Slots-18-基础篇-Cascading消除图标.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
   <si>
     <r>
       <rPr>
@@ -5341,7 +5341,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5456,6 +5456,10 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -6388,8 +6392,8 @@
       <c r="D4" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
-        <v>105</v>
+      <c r="A5" s="29">
+        <v>1</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>106</v>
@@ -6400,8 +6404,8 @@
       <c r="D5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
-        <v>108</v>
+      <c r="A6" s="29">
+        <v>2</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>109</v>
@@ -6412,8 +6416,8 @@
       <c r="D6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
-        <v>111</v>
+      <c r="A7" s="29">
+        <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>112</v>
@@ -6426,8 +6430,8 @@
       <c r="F7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>114</v>
+      <c r="A8" s="29">
+        <v>4</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>115</v>
@@ -6440,8 +6444,8 @@
       <c r="F8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
-        <v>117</v>
+      <c r="A9" s="29">
+        <v>5</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>118</v>
